--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalNormalTopic.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalNormalTopic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6379C14-9538-4FC4-8D39-F58F27ADD80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9408FF39-AFA2-44A0-9A6E-CD1751934AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8235" yWindow="6600" windowWidth="28800" windowHeight="14745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>单位名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,14 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>课程编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>课程名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>高新资质</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,34 +55,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>项目成果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>起始日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>完成日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2023年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2024年</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>研发人员名单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,7 +67,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>注：年份可以自定义新增列</t>
+    <t>注：年份列可以自定义新增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>课题编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>课题名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目成果形式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>研发起始日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>研发完成日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -208,7 +196,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -236,8 +224,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,24 +505,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
     <col min="5" max="5" width="12.125" customWidth="1"/>
     <col min="6" max="6" width="11.125" customWidth="1"/>
-    <col min="7" max="7" width="23.375" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="12.125" customWidth="1"/>
-    <col min="12" max="12" width="11.875" customWidth="1"/>
-    <col min="14" max="14" width="8.5" customWidth="1"/>
-    <col min="15" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="16" width="12.125" customWidth="1"/>
+    <col min="10" max="10" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -539,81 +530,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="2" spans="1:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="7"/>
       <c r="C2" s="8"/>
       <c r="D2" s="7"/>
-      <c r="L2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
+      <c r="L2" s="10"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
+      <c r="O6" s="9" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="L2:O2"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
